--- a/kuis.xlsx
+++ b/kuis.xlsx
@@ -1,107 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SDN 3 NGANTRU\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117031CC-CB45-422F-BF8E-74511C340F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="FormatKuis" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
-  <si>
-    <t>Pertanyaan</t>
-  </si>
-  <si>
-    <t>Pilihan A</t>
-  </si>
-  <si>
-    <t>Pilihan B</t>
-  </si>
-  <si>
-    <t>Pilihan C</t>
-  </si>
-  <si>
-    <t>Pilihan D</t>
-  </si>
-  <si>
-    <t>Jawaban</t>
-  </si>
-  <si>
-    <t>2/4</t>
-  </si>
-  <si>
-    <t>3/4</t>
-  </si>
-  <si>
-    <t>1/3</t>
-  </si>
-  <si>
-    <t>3/8</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>4/6</t>
-  </si>
-  <si>
-    <t>3/2</t>
-  </si>
-  <si>
-    <t>4/9</t>
-  </si>
-  <si>
-    <t>5/6</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>jawabben B</t>
-  </si>
-  <si>
-    <t>Jawaban A</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>q</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>jawaban C</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -131,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -470,117 +396,172 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="29.9140625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J5"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Waktu Mulai</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Waktu Selesai</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Durasi (Menit)</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Tipe</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Pertanyaan</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Pilihan A</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Pilihan B</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Pilihan C</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Pilihan D</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Jawaban</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-06-13 08:00</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-06-13 23:59</v>
+      </c>
+      <c r="C2">
+        <v>15</v>
+      </c>
+      <c r="D2" t="str">
+        <v>PG</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Berapakah hasil dari 1/2 ditambah 1/4?</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2/4</v>
+      </c>
+      <c r="G2" t="str">
+        <v>3/4</v>
+      </c>
+      <c r="H2" t="str">
+        <v>1/3</v>
+      </c>
+      <c r="I2" t="str">
+        <v>3/8</v>
+      </c>
+      <c r="J2" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>PGK</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Manakah di antara bilangan berikut yang merupakan bilangan prima? (Pilih semua yang benar)</v>
+      </c>
+      <c r="F3" t="str">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="G3" t="str">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H3" t="str">
         <v>5</v>
       </c>
+      <c r="I3" t="str">
+        <v>9</v>
+      </c>
+      <c r="J3" t="str">
+        <v>A;C</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>MENJODOHKAN</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Cocokkan nama provinsi dengan ibukotanya masing-masing:; 1. Jawa Timur; 2. Jawa Barat; 3. Jawa Tengah</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Bandung</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Surabaya</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Semarang</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Yogyakarta</v>
+      </c>
+      <c r="J4" t="str">
+        <v>B;A;C</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>ISIAN</v>
+      </c>
+      <c r="E5" t="str">
+        <v>SD Negeri 3 Ngantru bertempat di wilayah kecamatan?</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v>Ngantru | Kecamatan Ngantru | Kec. Ngantru</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F1 B3:F3 B2:F2" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/kuis.xlsx
+++ b/kuis.xlsx
@@ -1,41 +1,143 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SDN 3 NGANTRU\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F942CB3-4B91-439C-B3F2-A55F87631C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="FormatKuis" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
+  <si>
+    <t>Waktu Mulai</t>
+  </si>
+  <si>
+    <t>Waktu Selesai</t>
+  </si>
+  <si>
+    <t>Durasi (Menit)</t>
+  </si>
+  <si>
+    <t>Tipe</t>
+  </si>
+  <si>
+    <t>Pertanyaan</t>
+  </si>
+  <si>
+    <t>Pilihan A</t>
+  </si>
+  <si>
+    <t>Pilihan B</t>
+  </si>
+  <si>
+    <t>Pilihan C</t>
+  </si>
+  <si>
+    <t>Pilihan D</t>
+  </si>
+  <si>
+    <t>Jawaban</t>
+  </si>
+  <si>
+    <t>PG</t>
+  </si>
+  <si>
+    <t>Berapakah hasil dari 1/2 ditambah 1/4?</t>
+  </si>
+  <si>
+    <t>2/4</t>
+  </si>
+  <si>
+    <t>3/4</t>
+  </si>
+  <si>
+    <t>1/3</t>
+  </si>
+  <si>
+    <t>3/8</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>PGK</t>
+  </si>
+  <si>
+    <t>Manakah di antara bilangan berikut yang merupakan bilangan prima? (Pilih semua yang benar)</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>A;C</t>
+  </si>
+  <si>
+    <t>MENJODOHKAN</t>
+  </si>
+  <si>
+    <t>Cocokkan nama provinsi dengan ibukotanya masing-masing:; 1. Jawa Timur; 2. Jawa Barat; 3. Jawa Tengah</t>
+  </si>
+  <si>
+    <t>Bandung</t>
+  </si>
+  <si>
+    <t>Surabaya</t>
+  </si>
+  <si>
+    <t>Semarang</t>
+  </si>
+  <si>
+    <t>Yogyakarta</t>
+  </si>
+  <si>
+    <t>B;A;C</t>
+  </si>
+  <si>
+    <t>ISIAN</t>
+  </si>
+  <si>
+    <t>SD Negeri 3 Ngantru bertempat di wilayah kecamatan?</t>
+  </si>
+  <si>
+    <t>Ngantru | Kecamatan Ngantru | Kec. Ngantru</t>
+  </si>
+  <si>
+    <t>2026-06-14 08:00</t>
+  </si>
+  <si>
+    <t>2026-06-14 23:59</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +167,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,172 +506,174 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Waktu Mulai</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Waktu Selesai</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Durasi (Menit)</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Tipe</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Pertanyaan</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Pilihan A</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Pilihan B</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Pilihan C</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Pilihan D</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Jawaban</v>
+    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-06-13 08:00</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2026-06-13 23:59</v>
+    <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
       </c>
       <c r="C2">
         <v>15</v>
       </c>
-      <c r="D2" t="str">
-        <v>PG</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Berapakah hasil dari 1/2 ditambah 1/4?</v>
-      </c>
-      <c r="F2" t="str">
-        <v>2/4</v>
-      </c>
-      <c r="G2" t="str">
-        <v>3/4</v>
-      </c>
-      <c r="H2" t="str">
-        <v>1/3</v>
-      </c>
-      <c r="I2" t="str">
-        <v>3/8</v>
-      </c>
-      <c r="J2" t="str">
-        <v>B</v>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v/>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v>PGK</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Manakah di antara bilangan berikut yang merupakan bilangan prima? (Pilih semua yang benar)</v>
-      </c>
-      <c r="F3" t="str">
-        <v>2</v>
-      </c>
-      <c r="G3" t="str">
-        <v>4</v>
-      </c>
-      <c r="H3" t="str">
-        <v>5</v>
-      </c>
-      <c r="I3" t="str">
-        <v>9</v>
-      </c>
-      <c r="J3" t="str">
-        <v>A;C</v>
+    <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v/>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>MENJODOHKAN</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Cocokkan nama provinsi dengan ibukotanya masing-masing:; 1. Jawa Timur; 2. Jawa Barat; 3. Jawa Tengah</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Bandung</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Surabaya</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Semarang</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Yogyakarta</v>
-      </c>
-      <c r="J4" t="str">
-        <v>B;A;C</v>
+    <row r="4" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v>ISIAN</v>
-      </c>
-      <c r="E5" t="str">
-        <v>SD Negeri 3 Ngantru bertempat di wilayah kecamatan?</v>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v>Ngantru | Kecamatan Ngantru | Kec. Ngantru</v>
+    <row r="5" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
+    <ignoredError sqref="A1:J1 A3:J5 C2:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/kuis.xlsx
+++ b/kuis.xlsx
@@ -1,143 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SDN 3 NGANTRU\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CD71EB-9A18-462B-8E91-7764E688FAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="FormatKuis" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
-  <si>
-    <t>Waktu Mulai</t>
-  </si>
-  <si>
-    <t>Waktu Selesai</t>
-  </si>
-  <si>
-    <t>Durasi (Menit)</t>
-  </si>
-  <si>
-    <t>Tipe</t>
-  </si>
-  <si>
-    <t>Pertanyaan</t>
-  </si>
-  <si>
-    <t>Pilihan A</t>
-  </si>
-  <si>
-    <t>Pilihan B</t>
-  </si>
-  <si>
-    <t>Pilihan C</t>
-  </si>
-  <si>
-    <t>Pilihan D</t>
-  </si>
-  <si>
-    <t>Jawaban</t>
-  </si>
-  <si>
-    <t>PG</t>
-  </si>
-  <si>
-    <t>Berapakah hasil dari 1/2 ditambah 1/4?</t>
-  </si>
-  <si>
-    <t>2/4</t>
-  </si>
-  <si>
-    <t>3/4</t>
-  </si>
-  <si>
-    <t>1/3</t>
-  </si>
-  <si>
-    <t>3/8</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>PGK</t>
-  </si>
-  <si>
-    <t>Manakah di antara bilangan berikut yang merupakan bilangan prima? (Pilih semua yang benar)</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>A;C</t>
-  </si>
-  <si>
-    <t>MENJODOHKAN</t>
-  </si>
-  <si>
-    <t>Cocokkan nama provinsi dengan ibukotanya masing-masing:; 1. Jawa Timur; 2. Jawa Barat; 3. Jawa Tengah</t>
-  </si>
-  <si>
-    <t>Bandung</t>
-  </si>
-  <si>
-    <t>Surabaya</t>
-  </si>
-  <si>
-    <t>Semarang</t>
-  </si>
-  <si>
-    <t>Yogyakarta</t>
-  </si>
-  <si>
-    <t>B;A;C</t>
-  </si>
-  <si>
-    <t>ISIAN</t>
-  </si>
-  <si>
-    <t>SD Negeri 3 Ngantru bertempat di wilayah kecamatan?</t>
-  </si>
-  <si>
-    <t>Ngantru | Kecamatan Ngantru | Kec. Ngantru</t>
-  </si>
-  <si>
-    <t>2026-06-14 08:00</t>
-  </si>
-  <si>
-    <t>2026-06-14 23:59</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -167,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -506,177 +396,172 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="11.08203125" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Waktu Mulai</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Waktu Selesai</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Durasi (Menit)</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Tipe</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Pertanyaan</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Pilihan A</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Pilihan B</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Pilihan C</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Pilihan D</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Jawaban</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-06-13 08:00</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-06-13 23:59</v>
       </c>
       <c r="C2">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
+      <c r="D2" t="str">
+        <v>PG</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Berapakah hasil dari 1/2 ditambah 1/4?</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2/4</v>
+      </c>
+      <c r="G2" t="str">
+        <v>3/4</v>
+      </c>
+      <c r="H2" t="str">
+        <v>1/3</v>
+      </c>
+      <c r="I2" t="str">
+        <v>3/8</v>
+      </c>
+      <c r="J2" t="str">
+        <v>B</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>PGK</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Manakah di antara bilangan berikut yang merupakan bilangan prima? (Pilih semua yang benar)</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2</v>
+      </c>
+      <c r="G3" t="str">
+        <v>4</v>
+      </c>
+      <c r="H3" t="str">
+        <v>5</v>
+      </c>
+      <c r="I3" t="str">
+        <v>9</v>
+      </c>
+      <c r="J3" t="str">
+        <v>A;C</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" t="s">
-        <v>31</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>MENJODOHKAN</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Cocokkan nama provinsi dengan ibukotanya masing-masing:; 1. Jawa Timur; 2. Jawa Barat; 3. Jawa Tengah</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Bandung</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Surabaya</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Semarang</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Yogyakarta</v>
+      </c>
+      <c r="J4" t="str">
+        <v>B;A;C</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" t="s">
-        <v>34</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>ISIAN</v>
+      </c>
+      <c r="E5" t="str">
+        <v>SD Negeri 3 Ngantru bertempat di wilayah kecamatan?</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v>Ngantru | Kecamatan Ngantru | Kec. Ngantru</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J1 A3:J5 C2:J2" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/kuis.xlsx
+++ b/kuis.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="FormatKuis" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,31 +433,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-06-13 08:00</v>
+        <v>2026-08-06 12:31</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-13 23:59</v>
+        <v>2026-08-07 12:31</v>
       </c>
       <c r="C2">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="D2" t="str">
         <v>PG</v>
       </c>
       <c r="E2" t="str">
-        <v>Berapakah hasil dari 1/2 ditambah 1/4?</v>
+        <v>Bagian mata yang berfungsi mengatur jumlah cahaya yang masuk ke dalam bola mata adalah...</v>
       </c>
       <c r="F2" t="str">
-        <v>2/4</v>
+        <v>Iris</v>
       </c>
       <c r="G2" t="str">
-        <v>3/4</v>
+        <v>Pupil</v>
       </c>
       <c r="H2" t="str">
-        <v>1/3</v>
+        <v>Lensa</v>
       </c>
       <c r="I2" t="str">
-        <v>3/8</v>
+        <v>Retina</v>
       </c>
       <c r="J2" t="str">
         <v>B</v>
@@ -474,25 +474,25 @@
         <v/>
       </c>
       <c r="D3" t="str">
-        <v>PGK</v>
+        <v>PG</v>
       </c>
       <c r="E3" t="str">
-        <v>Manakah di antara bilangan berikut yang merupakan bilangan prima? (Pilih semua yang benar)</v>
+        <v>Bagian mata yang memberikan warna pada mata manusia seperti warna hitam, cokelat, atau biru adalah...</v>
       </c>
       <c r="F3" t="str">
-        <v>2</v>
+        <v>Iris</v>
       </c>
       <c r="G3" t="str">
-        <v>4</v>
+        <v>Kornea</v>
       </c>
       <c r="H3" t="str">
-        <v>5</v>
+        <v>Sklera</v>
       </c>
       <c r="I3" t="str">
-        <v>9</v>
+        <v>Pupil</v>
       </c>
       <c r="J3" t="str">
-        <v>A;C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="4">
@@ -506,25 +506,25 @@
         <v/>
       </c>
       <c r="D4" t="str">
-        <v>MENJODOHKAN</v>
+        <v>PG</v>
       </c>
       <c r="E4" t="str">
-        <v>Cocokkan nama provinsi dengan ibukotanya masing-masing:; 1. Jawa Timur; 2. Jawa Barat; 3. Jawa Tengah</v>
+        <v>Bayangan benda pada mata yang normal akan jatuh tepat pada bagian...</v>
       </c>
       <c r="F4" t="str">
-        <v>Bandung</v>
+        <v>Saraf optik</v>
       </c>
       <c r="G4" t="str">
-        <v>Surabaya</v>
+        <v>Lensa</v>
       </c>
       <c r="H4" t="str">
-        <v>Semarang</v>
+        <v>Retina</v>
       </c>
       <c r="I4" t="str">
-        <v>Yogyakarta</v>
+        <v>Kornea</v>
       </c>
       <c r="J4" t="str">
-        <v>B;A;C</v>
+        <v>C</v>
       </c>
     </row>
     <row r="5">
@@ -538,30 +538,670 @@
         <v/>
       </c>
       <c r="D5" t="str">
+        <v>PG</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Fungsi utama dari lensa mata adalah...</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Memberi warna pada mata</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Melindungi bagian dalam mata</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Mengirim sinyal ke otak</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Memfokuskan cahaya agar jatuh tepat di retina</v>
+      </c>
+      <c r="J5" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>PG</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Bagian bening yang terletak di lapisan paling luar mata dan berfungsi melindungi mata serta membantu pembiasan cahaya adalah...</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Kornea</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Retina</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Pupil</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Otot siliaris</v>
+      </c>
+      <c r="J6" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>PG</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Cairan kental dan transparan yang mengisi rongga di belakang lensa mata untuk menjaga bentuk bola mata adalah...</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Aqueous humor</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Vitreous humor</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Air mata</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Plasma mata</v>
+      </c>
+      <c r="J7" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>PG</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Saraf yang bertugas meneruskan informasi bayangan dari retina menuju ke otak disebut...</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Saraf motorik</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Saraf sensorik</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Saraf optik</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Saraf auditori</v>
+      </c>
+      <c r="J8" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>PG</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Kemampuan lensa mata untuk berubah menjadi cembung atau pipih sesuai jarak benda yang dilihat disebut daya...</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Oksidasi</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Refraksi</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Konvergensi</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Akomodasi</v>
+      </c>
+      <c r="J9" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v/>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>PG</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Bagian putih mata yang kuat dan berfungsi untuk melindungi struktur internal mata disebut...</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Sklera</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Koroid</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Iris</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Retina</v>
+      </c>
+      <c r="J10" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v/>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>PG</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Saat berada di ruangan yang sangat gelap, maka pupil akan...</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Mengecil</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Membesar</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Menghilang</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Tetap saja</v>
+      </c>
+      <c r="J11" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v/>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>PGK</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Manakah bagian mata berikut yang berperan dalam proses pembiasan cahaya? (Pilih dua jawaban benar)</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Kornea</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Iris</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Lensa mata</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Saraf optik</v>
+      </c>
+      <c r="J12" t="str">
+        <v>A;C</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v/>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>PGK</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Organ tambahan di sekitar mata yang berfungsi untuk melindungi mata dari keringat, debu, dan kotoran adalah... (Pilih dua jawaban benar)</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Lensa</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Alis mata</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Bulu mata</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Pupil</v>
+      </c>
+      <c r="J13" t="str">
+        <v>B;C</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v/>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>PGK</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Pilihlah pernyataan yang benar mengenai retina! (Pilih dua jawaban benar)</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Tempat terbentuknya bayangan</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Mengandung sel-sel yang peka terhadap cahaya</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Mengatur jumlah cahaya masuk</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Memberi warna pada bola mata</v>
+      </c>
+      <c r="J14" t="str">
+        <v>A;B</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v/>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>PGK</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Manakah dari berikut ini yang merupakan bagian dari lapisan bola mata? (Pilih dua jawaban benar)</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Sklera</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Kelopak mata</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Air mata</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Koroid</v>
+      </c>
+      <c r="J15" t="str">
+        <v>A;D</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v/>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v>PGK</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Apa yang terjadi pada mata ketika melihat benda dari jarak yang sangat dekat? (Pilih dua jawaban benar)</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Lensa memipih</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Lensa mencembung</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Otot siliaris berkontraksi</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Pupil menghilang</v>
+      </c>
+      <c r="J16" t="str">
+        <v>B;C</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v/>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>MENJODOHKAN</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Pasangkan bagian mata berikut dengan fungsinya yang tepat:; Kornea; Pupil; Iris</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Pemberi warna mata</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Lubang masuknya cahaya</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Pelindung bening terluar</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v>C;B;A</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v/>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>MENJODOHKAN</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Pasangkan organ indra mata berikut dengan deskripsinya:; Retina; Lensa; Saraf Optik</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Memfokuskan cahaya</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Layar penangkap bayangan</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Penyampai sinyal ke otak</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v>B;A;C</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v/>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>MENJODOHKAN</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Pasangkan bagian pelindung luar mata berikut dengan fungsinya:; Alis mata; Air mata; Bulu mata</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Menahan keringat masuk mata</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Menyaring debu dan kotoran</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Membasahi dan melumasi mata</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v>A;C;B</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v/>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>MENJODOHKAN</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Pasangkan bagian mata berikut dengan karakteristiknya:; Sklera; Vitreous humor; Bintik Buta</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Cairan kental seperti gel</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Area yang tidak peka cahaya</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Bagian putih dan keras</v>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v>C;A;B</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v/>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v>MENJODOHKAN</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Pasangkan istilah medis berikut dengan definisinya:; Daya Akomodasi; Bintik Kuning; Otot Siliaris</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Pengatur bentuk lensa mata</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Kemampuan mengubah fokus lensa</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Bagian retina paling peka cahaya</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v>B;C;A</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v/>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
         <v>ISIAN</v>
       </c>
-      <c r="E5" t="str">
-        <v>SD Negeri 3 Ngantru bertempat di wilayah kecamatan?</v>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v>Ngantru | Kecamatan Ngantru | Kec. Ngantru</v>
+      <c r="E22" t="str">
+        <v>Lubang kecil di tengah iris yang menjadi jalan masuknya cahaya ke dalam mata disebut...</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v>Pupil</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v/>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>ISIAN</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Kemampuan lensa mata untuk mencembung atau memipih disebut dengan daya...</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v>Akomodasi | daya akomodasi</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v/>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>ISIAN</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Lapisan terdalam bola mata yang berfungsi sebagai layar untuk menangkap bayangan adalah...</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v>Retina | selaput jala</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v/>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>ISIAN</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Bagian mata yang berfungsi menyalurkan informasi cahaya yang diterima ke otak adalah saraf...</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v>Optik | Penglihatan | Saraf Optik</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/kuis.xlsx
+++ b/kuis.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,31 +433,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-06 12:31</v>
+        <v>2026-08-18 12:36</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-08-07 12:31</v>
-      </c>
-      <c r="C2">
-        <v>45</v>
+        <v>2026-08-19 12:36</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
       </c>
       <c r="D2" t="str">
         <v>PG</v>
       </c>
       <c r="E2" t="str">
-        <v>Bagian mata yang berfungsi mengatur jumlah cahaya yang masuk ke dalam bola mata adalah...</v>
+        <v>Bagian mata yang berfungsi melindungi mata dari kotoran dan keringat adalah...</v>
       </c>
       <c r="F2" t="str">
-        <v>Iris</v>
+        <v>Lensa mata</v>
       </c>
       <c r="G2" t="str">
+        <v>Alis dan kelopak mata</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Retina</v>
+      </c>
+      <c r="I2" t="str">
         <v>Pupil</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Lensa</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Retina</v>
       </c>
       <c r="J2" t="str">
         <v>B</v>
@@ -477,22 +477,22 @@
         <v>PG</v>
       </c>
       <c r="E3" t="str">
-        <v>Bagian mata yang memberikan warna pada mata manusia seperti warna hitam, cokelat, atau biru adalah...</v>
+        <v>Bagian mata yang mengatur jumlah cahaya yang masuk ke dalam mata disebut...</v>
       </c>
       <c r="F3" t="str">
-        <v>Iris</v>
+        <v>Sklera</v>
       </c>
       <c r="G3" t="str">
         <v>Kornea</v>
       </c>
       <c r="H3" t="str">
-        <v>Sklera</v>
+        <v>Pupil</v>
       </c>
       <c r="I3" t="str">
-        <v>Pupil</v>
+        <v>Saraf optik</v>
       </c>
       <c r="J3" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="4">
@@ -509,22 +509,22 @@
         <v>PG</v>
       </c>
       <c r="E4" t="str">
-        <v>Bayangan benda pada mata yang normal akan jatuh tepat pada bagian...</v>
+        <v>Lapisan tipis di bagian belakang mata yang berfungsi menangkap bayangan benda dan diteruskan ke sel optik menuju otak adalah...</v>
       </c>
       <c r="F4" t="str">
-        <v>Saraf optik</v>
+        <v>Retina</v>
       </c>
       <c r="G4" t="str">
+        <v>Iris</v>
+      </c>
+      <c r="H4" t="str">
         <v>Lensa</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Retina</v>
       </c>
       <c r="I4" t="str">
         <v>Kornea</v>
       </c>
       <c r="J4" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="5">
@@ -541,19 +541,19 @@
         <v>PG</v>
       </c>
       <c r="E5" t="str">
-        <v>Fungsi utama dari lensa mata adalah...</v>
+        <v>Warna mata seseorang, seperti cokelat atau biru, ditentukan oleh bagian mata yang bernama...</v>
       </c>
       <c r="F5" t="str">
-        <v>Memberi warna pada mata</v>
+        <v>Pupil</v>
       </c>
       <c r="G5" t="str">
-        <v>Melindungi bagian dalam mata</v>
+        <v>Sklera</v>
       </c>
       <c r="H5" t="str">
-        <v>Mengirim sinyal ke otak</v>
+        <v>Lensa</v>
       </c>
       <c r="I5" t="str">
-        <v>Memfokuskan cahaya agar jatuh tepat di retina</v>
+        <v>Iris</v>
       </c>
       <c r="J5" t="str">
         <v>D</v>
@@ -573,22 +573,22 @@
         <v>PG</v>
       </c>
       <c r="E6" t="str">
-        <v>Bagian bening yang terletak di lapisan paling luar mata dan berfungsi melindungi mata serta membantu pembiasan cahaya adalah...</v>
+        <v>Bagian bening dalam bola mata  yang berfungsi melindungi mata dari debu disebut...</v>
       </c>
       <c r="F6" t="str">
+        <v>Retina</v>
+      </c>
+      <c r="G6" t="str">
         <v>Kornea</v>
       </c>
-      <c r="G6" t="str">
-        <v>Retina</v>
-      </c>
       <c r="H6" t="str">
+        <v>Sklera</v>
+      </c>
+      <c r="I6" t="str">
         <v>Pupil</v>
       </c>
-      <c r="I6" t="str">
-        <v>Otot siliaris</v>
-      </c>
       <c r="J6" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="7">
@@ -605,22 +605,22 @@
         <v>PG</v>
       </c>
       <c r="E7" t="str">
-        <v>Cairan kental dan transparan yang mengisi rongga di belakang lensa mata untuk menjaga bentuk bola mata adalah...</v>
+        <v>Lensa mata memiliki kemampuan untuk menebal dan menipis yang disebut daya...</v>
       </c>
       <c r="F7" t="str">
-        <v>Aqueous humor</v>
+        <v>Akomodasi</v>
       </c>
       <c r="G7" t="str">
-        <v>Vitreous humor</v>
+        <v>Refraksi</v>
       </c>
       <c r="H7" t="str">
-        <v>Air mata</v>
+        <v>Adaptasi</v>
       </c>
       <c r="I7" t="str">
-        <v>Plasma mata</v>
+        <v>Visualisasi</v>
       </c>
       <c r="J7" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="8">
@@ -637,19 +637,19 @@
         <v>PG</v>
       </c>
       <c r="E8" t="str">
-        <v>Saraf yang bertugas meneruskan informasi bayangan dari retina menuju ke otak disebut...</v>
+        <v>Setelah cahaya ditangkap oleh retina, informasi akan diteruskan ke otak melalui...</v>
       </c>
       <c r="F8" t="str">
-        <v>Saraf motorik</v>
+        <v>Otot mata</v>
       </c>
       <c r="G8" t="str">
-        <v>Saraf sensorik</v>
+        <v>Pupil</v>
       </c>
       <c r="H8" t="str">
         <v>Saraf optik</v>
       </c>
       <c r="I8" t="str">
-        <v>Saraf auditori</v>
+        <v>Cairan mata</v>
       </c>
       <c r="J8" t="str">
         <v>C</v>
@@ -669,19 +669,19 @@
         <v>PG</v>
       </c>
       <c r="E9" t="str">
-        <v>Kemampuan lensa mata untuk berubah menjadi cembung atau pipih sesuai jarak benda yang dilihat disebut daya...</v>
+        <v>Cahaya masuk ke mata secara berurutan mulai dari...</v>
       </c>
       <c r="F9" t="str">
-        <v>Oksidasi</v>
+        <v>Retina - Lensa - Pupil - Kornea</v>
       </c>
       <c r="G9" t="str">
-        <v>Refraksi</v>
+        <v>Pupil - Kornea - Lensa - Retina</v>
       </c>
       <c r="H9" t="str">
-        <v>Konvergensi</v>
+        <v>Lensa - Pupil - Kornea - Retina</v>
       </c>
       <c r="I9" t="str">
-        <v>Akomodasi</v>
+        <v>Kornea - Pupil - Lensa - Retina</v>
       </c>
       <c r="J9" t="str">
         <v>D</v>
@@ -701,22 +701,22 @@
         <v>PG</v>
       </c>
       <c r="E10" t="str">
-        <v>Bagian putih mata yang kuat dan berfungsi untuk melindungi struktur internal mata disebut...</v>
+        <v>Bagian mata yang berwarna putih dan berfungsi melindungi bagian dalam bola mata adalah...</v>
       </c>
       <c r="F10" t="str">
+        <v>Iris</v>
+      </c>
+      <c r="G10" t="str">
         <v>Sklera</v>
       </c>
-      <c r="G10" t="str">
-        <v>Koroid</v>
-      </c>
       <c r="H10" t="str">
-        <v>Iris</v>
+        <v>Kornea</v>
       </c>
       <c r="I10" t="str">
         <v>Retina</v>
       </c>
       <c r="J10" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="11">
@@ -733,22 +733,22 @@
         <v>PG</v>
       </c>
       <c r="E11" t="str">
-        <v>Saat berada di ruangan yang sangat gelap, maka pupil akan...</v>
+        <v>Apa yang terjadi pada pupil saat kita berada di tempat yang sangat terang?</v>
       </c>
       <c r="F11" t="str">
-        <v>Mengecil</v>
+        <v>Pupil mengecil</v>
       </c>
       <c r="G11" t="str">
-        <v>Membesar</v>
+        <v>Pupil membesar</v>
       </c>
       <c r="H11" t="str">
-        <v>Menghilang</v>
+        <v>Pupil berubah warna</v>
       </c>
       <c r="I11" t="str">
-        <v>Tetap saja</v>
+        <v>Pupil menghilang</v>
       </c>
       <c r="J11" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="12">
@@ -765,22 +765,22 @@
         <v>PGK</v>
       </c>
       <c r="E12" t="str">
-        <v>Manakah bagian mata berikut yang berperan dalam proses pembiasan cahaya? (Pilih dua jawaban benar)</v>
+        <v>Pilihlah bagian-bagian mata yang berfungsi untuk melindungi mata dari gangguan luar!</v>
       </c>
       <c r="F12" t="str">
-        <v>Kornea</v>
+        <v>Kornea mata</v>
       </c>
       <c r="G12" t="str">
-        <v>Iris</v>
+        <v>Alis mata</v>
       </c>
       <c r="H12" t="str">
-        <v>Lensa mata</v>
+        <v>Bulu mata</v>
       </c>
       <c r="I12" t="str">
         <v>Saraf optik</v>
       </c>
       <c r="J12" t="str">
-        <v>A;C</v>
+        <v>B;C</v>
       </c>
     </row>
     <row r="13">
@@ -797,22 +797,22 @@
         <v>PGK</v>
       </c>
       <c r="E13" t="str">
-        <v>Organ tambahan di sekitar mata yang berfungsi untuk melindungi mata dari keringat, debu, dan kotoran adalah... (Pilih dua jawaban benar)</v>
+        <v>Pernyataan mana yang benar mengenai cara kerja mata saat melihat benda?</v>
       </c>
       <c r="F13" t="str">
-        <v>Lensa</v>
+        <v>Mata mengeluarkan cahaya sendiri untuk melihat</v>
       </c>
       <c r="G13" t="str">
-        <v>Alis mata</v>
+        <v>Cahaya dipantulkan oleh benda menuju mata</v>
       </c>
       <c r="H13" t="str">
-        <v>Bulu mata</v>
+        <v>Bayangan benda di retina tidak diteruskan ke saraf optik</v>
       </c>
       <c r="I13" t="str">
-        <v>Pupil</v>
+        <v>Lensa memfokuskan cahaya agar jatuh tepat di retina</v>
       </c>
       <c r="J13" t="str">
-        <v>B;C</v>
+        <v>B;D</v>
       </c>
     </row>
     <row r="14">
@@ -829,22 +829,22 @@
         <v>PGK</v>
       </c>
       <c r="E14" t="str">
-        <v>Pilihlah pernyataan yang benar mengenai retina! (Pilih dua jawaban benar)</v>
+        <v>Manakah dari bagian berikut yang termasuk bagian dari mata dalam ?</v>
       </c>
       <c r="F14" t="str">
-        <v>Tempat terbentuknya bayangan</v>
+        <v>Retina</v>
       </c>
       <c r="G14" t="str">
-        <v>Mengandung sel-sel yang peka terhadap cahaya</v>
+        <v>Alis</v>
       </c>
       <c r="H14" t="str">
-        <v>Mengatur jumlah cahaya masuk</v>
+        <v>Lensa</v>
       </c>
       <c r="I14" t="str">
-        <v>Memberi warna pada bola mata</v>
+        <v>Bulu mata</v>
       </c>
       <c r="J14" t="str">
-        <v>A;B</v>
+        <v>A;C</v>
       </c>
     </row>
     <row r="15">
@@ -861,22 +861,22 @@
         <v>PGK</v>
       </c>
       <c r="E15" t="str">
-        <v>Manakah dari berikut ini yang merupakan bagian dari lapisan bola mata? (Pilih dua jawaban benar)</v>
+        <v>Apa  fungsi iris?</v>
       </c>
       <c r="F15" t="str">
-        <v>Sklera</v>
+        <v>Memberi warna pada mata</v>
       </c>
       <c r="G15" t="str">
-        <v>Kelopak mata</v>
+        <v>Melindungi mata</v>
       </c>
       <c r="H15" t="str">
-        <v>Air mata</v>
+        <v>Mengatur besar kecil cahaya yang masuk ke mata</v>
       </c>
       <c r="I15" t="str">
-        <v>Koroid</v>
+        <v>Menghasilkan air mata</v>
       </c>
       <c r="J15" t="str">
-        <v>A;D</v>
+        <v>A;C</v>
       </c>
     </row>
     <row r="16">
@@ -893,22 +893,22 @@
         <v>PGK</v>
       </c>
       <c r="E16" t="str">
-        <v>Apa yang terjadi pada mata ketika melihat benda dari jarak yang sangat dekat? (Pilih dua jawaban benar)</v>
+        <v>Pilihlah urutan yang benar dari alur masuknya cahaya sebelum sampai ke otak!</v>
       </c>
       <c r="F16" t="str">
-        <v>Lensa memipih</v>
+        <v>Kornea kemudian ke Pupil</v>
       </c>
       <c r="G16" t="str">
-        <v>Lensa mencembung</v>
+        <v>Lensa kemudian ke Retina</v>
       </c>
       <c r="H16" t="str">
-        <v>Otot siliaris berkontraksi</v>
+        <v>Saraf optik kemudian ke Kornea</v>
       </c>
       <c r="I16" t="str">
-        <v>Pupil menghilang</v>
+        <v>Retina kemudian ke Pupil</v>
       </c>
       <c r="J16" t="str">
-        <v>B;C</v>
+        <v>A;B</v>
       </c>
     </row>
     <row r="17">
@@ -925,22 +925,22 @@
         <v>MENJODOHKAN</v>
       </c>
       <c r="E17" t="str">
-        <v>Pasangkan bagian mata berikut dengan fungsinya yang tepat:; Kornea; Pupil; Iris</v>
+        <v>Pasangkan bagian mata berikut dengan fungsi utamanya yang tepat!; Kornea; Iris; Saraf optik</v>
       </c>
       <c r="F17" t="str">
-        <v>Pemberi warna mata</v>
+        <v>Mengirim sinyal visual ke otak</v>
       </c>
       <c r="G17" t="str">
-        <v>Lubang masuknya cahaya</v>
+        <v>Tempat masuknya cahaya pertama kali</v>
       </c>
       <c r="H17" t="str">
-        <v>Pelindung bening terluar</v>
+        <v>Mengatur warna mata dan ukuran pupil</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>Melindungi dari air hujan</v>
       </c>
       <c r="J17" t="str">
-        <v>C;B;A</v>
+        <v>B;C;A</v>
       </c>
     </row>
     <row r="18">
@@ -957,22 +957,22 @@
         <v>MENJODOHKAN</v>
       </c>
       <c r="E18" t="str">
-        <v>Pasangkan organ indra mata berikut dengan deskripsinya:; Retina; Lensa; Saraf Optik</v>
+        <v>Pasangkan komponen pelindung mata dengan kegunaannya!; Alis mata; Bulu mata; Kelenjar air mata</v>
       </c>
       <c r="F18" t="str">
-        <v>Memfokuskan cahaya</v>
+        <v>Menyaring debu dan kotoran</v>
       </c>
       <c r="G18" t="str">
-        <v>Layar penangkap bayangan</v>
+        <v>Membasahi dan membunuh kuman</v>
       </c>
       <c r="H18" t="str">
-        <v>Penyampai sinyal ke otak</v>
+        <v>Menahan keringat agar tidak masuk ke mata</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>Meneruskan bayangan ke saraf optik</v>
       </c>
       <c r="J18" t="str">
-        <v>B;A;C</v>
+        <v>C;A;B</v>
       </c>
     </row>
     <row r="19">
@@ -989,22 +989,22 @@
         <v>MENJODOHKAN</v>
       </c>
       <c r="E19" t="str">
-        <v>Pasangkan bagian pelindung luar mata berikut dengan fungsinya:; Alis mata; Air mata; Bulu mata</v>
+        <v>Pasangkan bagian mata dengan lokasinya!; Pupil; Sklera; Retina</v>
       </c>
       <c r="F19" t="str">
-        <v>Menahan keringat masuk mata</v>
+        <v>Lapisan luar yang berwarna putih</v>
       </c>
       <c r="G19" t="str">
-        <v>Menyaring debu dan kotoran</v>
+        <v>Lubang di tengah iris</v>
       </c>
       <c r="H19" t="str">
-        <v>Membasahi dan melumasi mata</v>
+        <v>Lapisan terdalam di belakang mata</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>Bagian luar mata</v>
       </c>
       <c r="J19" t="str">
-        <v>A;C;B</v>
+        <v>B;A;C</v>
       </c>
     </row>
     <row r="20">
@@ -1021,22 +1021,22 @@
         <v>MENJODOHKAN</v>
       </c>
       <c r="E20" t="str">
-        <v>Pasangkan bagian mata berikut dengan karakteristiknya:; Sklera; Vitreous humor; Bintik Buta</v>
+        <v>Pasangkan proses berikut dengan bagian mata yang bertanggung jawab!; Memfokuskan cahaya; Menangkap bayangan; Meneruskan cahaya ke dalam lensa mata</v>
       </c>
       <c r="F20" t="str">
-        <v>Cairan kental seperti gel</v>
+        <v>Kornea</v>
       </c>
       <c r="G20" t="str">
-        <v>Area yang tidak peka cahaya</v>
+        <v>Retina</v>
       </c>
       <c r="H20" t="str">
-        <v>Bagian putih dan keras</v>
+        <v>Lensa</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>Iris</v>
       </c>
       <c r="J20" t="str">
-        <v>C;A;B</v>
+        <v>C;B;A</v>
       </c>
     </row>
     <row r="21">
@@ -1053,22 +1053,22 @@
         <v>MENJODOHKAN</v>
       </c>
       <c r="E21" t="str">
-        <v>Pasangkan istilah medis berikut dengan definisinya:; Daya Akomodasi; Bintik Kuning; Otot Siliaris</v>
+        <v>Pasangkan kondisi cahaya dengan reaksi pupil!; Cahaya terang; Cahaya redup; Cahaya normal</v>
       </c>
       <c r="F21" t="str">
-        <v>Pengatur bentuk lensa mata</v>
+        <v>Pupil melebar/membesar</v>
       </c>
       <c r="G21" t="str">
-        <v>Kemampuan mengubah fokus lensa</v>
+        <v>Pupil mengecil</v>
       </c>
       <c r="H21" t="str">
-        <v>Bagian retina paling peka cahaya</v>
+        <v>Pupil ukuran stabil</v>
       </c>
       <c r="I21" t="str">
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>B;C;A</v>
+        <v>B;A;C</v>
       </c>
     </row>
     <row r="22">
@@ -1085,7 +1085,7 @@
         <v>ISIAN</v>
       </c>
       <c r="E22" t="str">
-        <v>Lubang kecil di tengah iris yang menjadi jalan masuknya cahaya ke dalam mata disebut...</v>
+        <v>Rabun jauh (miopi) dapat dibantu dengan kacamata ber lensa ?</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1100,7 +1100,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>Pupil</v>
+        <v>cembung | menebal</v>
       </c>
     </row>
     <row r="23">
@@ -1117,7 +1117,7 @@
         <v>ISIAN</v>
       </c>
       <c r="E23" t="str">
-        <v>Kemampuan lensa mata untuk mencembung atau memipih disebut dengan daya...</v>
+        <v>Bagian mata yang berfungsi mengirimkan informasi visual dari retina ke otak adalah ...</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -1132,7 +1132,7 @@
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>Akomodasi | daya akomodasi</v>
+        <v>saraf optik | saraf mata</v>
       </c>
     </row>
     <row r="24">
@@ -1149,7 +1149,7 @@
         <v>ISIAN</v>
       </c>
       <c r="E24" t="str">
-        <v>Lapisan terdalam bola mata yang berfungsi sebagai layar untuk menangkap bayangan adalah...</v>
+        <v>Lubang kecil ditengah iris sebagai tempat masuknya cahaya ke dalam bola mata disebut ...</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -1164,7 +1164,7 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>Retina | selaput jala</v>
+        <v>pupil</v>
       </c>
     </row>
     <row r="25">
@@ -1181,7 +1181,7 @@
         <v>ISIAN</v>
       </c>
       <c r="E25" t="str">
-        <v>Bagian mata yang berfungsi menyalurkan informasi cahaya yang diterima ke otak adalah saraf...</v>
+        <v>Agar kita bisa melihat, cahaya harus ... oleh benda lalu masuk ke mata kita.</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -1196,12 +1196,44 @@
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>Optik | Penglihatan | Saraf Optik</v>
+        <v>dipantulkan | memantul</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v/>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v>ISIAN</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Lapisan paling luar mata yang jernih dan berfungsi sebagai jendela masuknya cahaya adalah ...</v>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v>kornea</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J26"/>
   </ignoredErrors>
 </worksheet>
 </file>